--- a/extenbooks/S603.xlsx
+++ b/extenbooks/S603.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S603.xlsx
+++ b/extenbooks/S603.xlsx
@@ -793,10 +793,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–2025</t>
+          <t>1952-1989</t>
         </is>
       </c>
     </row>
@@ -954,252 +954,262 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PROXY DISCLOSURE</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TRUE — this series is NOT a direct replication of the book concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>proxy_basis</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>&lt;not specified&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>proxy_disclosure</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Matrix-derived or surrogate construction; consult docs/series/S603_DPR.md for full disclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S603-A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S603 — Property Tax Workers</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix Ch6 — `Table6_1_TaxAccounts.csv`, column `property_tax_workers`</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions_usd</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Content Type**: time_series</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>**Status**: calculated</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t># S603 — Property Tax Workers</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Chapter**: 6 — The Net Social Wage</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Worker share of property and motor-vehicle taxes (apportioned by income class).</t>
+          <t>**Source Table**: Appendix Ch6 — `Table6_1_TaxAccounts.csv`, column `property_tax_workers`</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Units**: billions_usd</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>**Content Type**: time_series</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/Table6_1_TaxAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Worker share of property and motor-vehicle taxes (apportioned by income class).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>`data/source/book_tables/Table6_1_TaxAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1952=4.19B; 1989=74.93B</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S603_property_tax_workers.py`. Both endpoints PASS.</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>data/source/book_tables/Table6_1_TaxAccounts.csv</t>
+          <t>1952=4.19B; 1989=74.93B</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S603_property_tax_workers.py</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S603.csv</t>
+          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S603_property_tax_workers.py`. Both endpoints PASS.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S603_property_tax_workers.py</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S603.csv</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S603_property_tax_workers.py</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -1211,47 +1221,103 @@
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>data/source/book_tables/Table6_1_TaxAccounts.csv</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S603_property_tax_workers.py</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └── data/intermediate/S603.csv</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S603_property_tax_workers.py</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S603.csv</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S603_property_tax_workers.py</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1268,12 +1334,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1296,162 +1362,261 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Property taxes allocated to workers based on worker housing share. Workers bear property taxes on residential property they own or rent (renters bear property tax via higher rents). The worker share is computed as the ratio of worker-occupied housing value to total property tax base.</t>
+          <t>Group II - Personal taxes (workers' share = labor income/personal income): Personal income taxes (federal and state); Motor vehicle licenses; Property taxes (primarily on homes - adjusted for homeowners only); Other taxes and nontaxes.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Appendix N (Tax Classification, Group II), page 357; HDARP chunk_38 lines 262-266</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Total property tax revenue from NIPA Table 3.3 (State and Local Government Current Receipts, line 9 — property taxes). Worker housing share derived from Census housing data and homeownership rates cross-referenced with income distribution.</t>
+          <t>Property taxes: Only homeowner portion, then × labor share (Tonak 1984, chap. IV, apx. I).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BEA NIPA Table 3.3; Census Bureau housing data</t>
+          <t>ST_1994, Appendix N methodology notes; HDARP chunk_38 line 325</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>methodological_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Property tax incidence on renters is a standard assumption: landlords pass property taxes through to tenants via rental prices. Since workers are disproportionately renters, a significant portion of residential property tax falls on workers. Commercial and industrial property taxes are excluded from the worker allocation.</t>
+          <t>Personal property taxes 1964: total 8.4, labor portion 6.1 (× 0.727 homeowner adjustment); Motor vehicle taxes and licenses 1964: total 1.1, labor portion 0.8 (× 0.727).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6</t>
+          <t>ST_1994, Table N.1 Group II line items 1964; HDARP chunk_38 lines 304-305</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>empirical_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Property taxes are the smallest of the three direct tax components for workers (after personal income tax and social insurance). Their share of total worker tax burden declined over the period as social insurance taxes grew. State/local property tax revenue is the primary source; federal property taxes are negligible.</t>
+          <t>It is important to note that the taxes we estimate are those flowing directly out of total employee compensation (the purchase price of labor power to individual capitalists). From a Marxian point of view, we are concerned with the actual flows of royalties into, and out of, the actual flow of variable capital.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Section 5.9 (Scope of analysis), page 137; HDARP chunk_16 lines 95-97</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>decision_log_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEC-008 (2026-04-09): Tax allocation methodology confirmed. Property tax worker share is allocated via the income-proportional (housing share) method consistent with the NRYwp framework verified in Section 3.3 (pages 63-65). The broader principle — that taxes borne by productive workers reduce V* — applies here. P09 implementation verified.</t>
+          <t>Property taxes (primarily on homes - adjusted for homeowners only) ... Personal property taxes 1964: total 8.4, labor portion 6.1 (× 0.727 homeowner adjustment).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NickyData/DECISION_LOG.md, DEC-008</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>ST_1994, Appendix N (Group II) + Table N.1; KB chunk_38 lines 265, 305</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Motor vehicle taxes and licenses 1964: total 1.1, labor portion 0.8 (x 0.727).</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1; KB chunk_38 line 304</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Worker share of property taxes allocated via worker housing share applied to state/local property tax revenue from NIPA Table 3.3 line 9. Includes pass-through of property taxes to renters. Method consistent with DEC-008 tax allocation framework.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>Property taxes: Only homeowner portion, then × labor share (Tonak 1984, chap. IV, apx. I).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N methodology notes; KB chunk_38 line 325</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other taxes and nontaxes (passport fees, fines, etc. - very small) belong to Group II personal taxes (workers' share = labor income/personal income).</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Tax Classification, Group II); KB chunk_38 lines 262-266</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Group II (labor share = 0.727): Personal income taxes (federal + state) 50.0 -&gt; 36.4; Other taxes and nontaxes 3.8 -&gt; 2.8; Motor vehicle taxes and licenses 1.1 -&gt; 0.8; Personal property taxes 8.4 -&gt; 6.1 (homeowner adjustment).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 Group II line items 1964; KB chunk_38 lines 301-305</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Worker housing share proxy may not capture regional variation in property tax rates</t>
+          <t>Property taxes allocated to workers based on worker housing share. Workers bear property taxes on residential property they own or rent (renters bear property tax via higher rents). The worker share is computed as the ratio of worker-occupied housing value to total property tax base.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Renter pass-through assumption is debated in public finance literature</t>
+          <t>Total property tax revenue from NIPA Table 3.3 (State and Local Government Current Receipts, line 9 — property taxes). Worker housing share derived from Census housing data and homeownership rates cross-referenced with income distribution.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BEA NIPA Table 3.3; Census Bureau housing data</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>methodological_note</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Commercial property tax exclusion requires clean residential/commercial split</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>Property tax incidence on renters is a standard assumption: landlords pass property taxes through to tenants via rental prices. Since workers are disproportionately renters, a significant portion of residential property tax falls on workers. Commercial and industrial property taxes are excluded from the worker allocation.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>empirical_finding</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Property taxes are the smallest of the three direct tax components for workers (after personal income tax and social insurance). Their share of total worker tax burden declined over the period as social insurance taxes grew. State/local property tax revenue is the primary source; federal property taxes are negligible.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CHAPTER_6_INVESTIGATION.md</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>S601</t>
-        </is>
-      </c>
-    </row>
+          <t>decision_log_note</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[internal-decision-record] (2026-04-09): Tax allocation methodology confirmed. Property tax worker share is allocated via the income-proportional (housing share) method consistent with the NRYwp framework verified in Section 3.3 (pages 63-65). The broader principle — that taxes borne by productive workers reduce V* — applies here. P09 implementation verified.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[internal-decision-log], [internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>S602</t>
-        </is>
-      </c>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S604</t>
+          <t>Property taxes (primarily on homes - adjusted for homeowners only) ... Personal property taxes 1964: total 8.4, labor portion 6.1 (× 0.727 homeowner adjustment).</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Group II) + Table N.1; KB chunk_38 lines 265, 305</t>
         </is>
       </c>
     </row>
@@ -1459,37 +1624,166 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Motor vehicle taxes and licenses 1964: total 1.1, labor portion 0.8 (x 0.727).</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1; KB chunk_38 line 304</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Property taxes: Only homeowner portion, then × labor share (Tonak 1984, chap. IV, apx. I).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N methodology notes; KB chunk_38 line 325</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other taxes and nontaxes (passport fees, fines, etc. - very small) belong to Group II personal taxes (workers' share = labor income/personal income).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Tax Classification, Group II); KB chunk_38 lines 262-266</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Group II (labor share = 0.727): Personal income taxes (federal + state) 50.0 -&gt; 36.4; Other taxes and nontaxes 3.8 -&gt; 2.8; Motor vehicle taxes and licenses 1.1 -&gt; 0.8; Personal property taxes 8.4 -&gt; 6.1 (homeowner adjustment).</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 Group II line items 1964; KB chunk_38 lines 301-305</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Worker share of property taxes allocated via worker housing share applied to state/local property tax revenue from NIPA Table 3.3 line 9. Includes pass-through of property taxes to renters. Method consistent with [internal-decision-record] tax allocation framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Worker housing share proxy may not capture regional variation in property tax rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Renter pass-through assumption is debated in public finance literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Commercial property tax exclusion requires clean residential/commercial split</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S601</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S602</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>S604</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>S607</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
         </is>
@@ -1506,11 +1800,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1562,59 +1856,143 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EXTENSION</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>null — series does not extend beyond book period</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>PROXY CONSTRUCTION NOTICE</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>proxy_basis</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>&lt;not specified&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>proxy_disclosure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>expected_range</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>[0, 500]</t>
-        </is>
-      </c>
-    </row>
+          <t>Series is a proxy, not a direct replication. See DPR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>null - series does not extend beyond book period</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{"1952": 4.1925, "1989": 74.9315}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>expected_range</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[0, 500]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>level_series</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
